--- a/output/pdf_financials_xlsx/BLOK.H.xlsx
+++ b/output/pdf_financials_xlsx/BLOK.H.xlsx
@@ -6204,19 +6204,19 @@
         <v>9.643884999999999</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>10.364515</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.973029</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>12.623456</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>11.551531</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>11.551531</v>
       </c>
     </row>
     <row r="93">
@@ -6801,10 +6801,10 @@
         <v>0.261874</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>-0.115531</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>0.147871</v>
       </c>
       <c r="P103" s="3" t="n">
         <v>0</v>
@@ -6975,10 +6975,10 @@
         <v>-2.149266</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.198821</v>
+        <v>0.08329</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.026569</v>
+        <v>0.17444</v>
       </c>
       <c r="P106" s="3" t="n">
         <v>-0.203986</v>
@@ -9457,7 +9457,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -14871,7 +14875,11 @@
           <t>Receivables, prepaids and deposits</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -15580,7 +15588,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -34845,7 +34857,11 @@
           <t>Receivables, prepaids and deposits</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BLOK.H.xlsx
+++ b/output/pdf_financials_xlsx/BLOK.H.xlsx
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.253197</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013867</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022434</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1163,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000702</v>
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
@@ -2143,16 +2143,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-34.399552</v>
+        <v>-34.146355</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-7.561953</v>
+        <v>-7.548086</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1.494419</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.373914</v>
+        <v>2.396348</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>1.66346</v>
@@ -2185,7 +2185,7 @@
         <v>-1.023568</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.354316</v>
+        <v>0.355018</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2267,16 +2267,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-32.730644</v>
+        <v>-32.477447</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.55731</v>
+        <v>-7.543443</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>1.994612</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.708167</v>
+        <v>3.730601</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>2.874419</v>
@@ -2309,7 +2309,7 @@
         <v>-1.023568</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.354316</v>
+        <v>0.355018</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2587,40 +2587,40 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.918115</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.918115</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.508028</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.210369</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.239193</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.806265</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.011004</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.07657899999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.169872</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>6.840435</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>4.691169</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.052937</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.002785</v>
@@ -2707,40 +2707,40 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.918115</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.918115</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.508028</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.210369</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.239193</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.806265</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.011004</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.07657899999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.169872</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>6.840435</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>4.691169</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.052937</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0.002785</v>
@@ -3427,37 +3427,37 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.970879</v>
+        <v>0.052764</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.59997</v>
+        <v>1.091942</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.954159</v>
+        <v>0.74379</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.541248</v>
+        <v>0.302055</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.700441</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.011004</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.216439</v>
+        <v>0.13986</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.169872</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>7.134446</v>
+        <v>0.294011</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.723306</v>
+        <v>0.032137</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -23592,7 +23592,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -25299,7 +25299,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -51772,7 +51772,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -63691,7 +63691,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E550" s="5" t="n">
@@ -63790,7 +63790,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E551" s="5" t="n">
